--- a/artfynd/A 46602-2023 artfynd.xlsx
+++ b/artfynd/A 46602-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46602-2023 artfynd.xlsx
+++ b/artfynd/A 46602-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111315331</v>
+        <v>111315332</v>
       </c>
       <c r="B2" t="n">
-        <v>102869</v>
+        <v>104315</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419169.4996277513</v>
+        <v>419169</v>
       </c>
       <c r="R2" t="n">
-        <v>6206612.386244721</v>
+        <v>6206612</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,26 +754,16 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -782,6 +772,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bruknngsväg</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -790,131 +785,10 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Via Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>111315332</v>
-      </c>
-      <c r="B3" t="n">
-        <v>104315</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220711</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lungrot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Blitum bonus-henricus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Rchb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Nygård, 150 m öster , Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>419169</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6206612</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hässleholm</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Häglinge</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>M-Hlm-0039</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1990-05-21</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1990-05-21</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bruknngsväg</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 46602-2023 artfynd.xlsx
+++ b/artfynd/A 46602-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111315332</v>
+        <v>86370347</v>
       </c>
       <c r="B2" t="n">
-        <v>104315</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220711</v>
+        <v>134</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lungrot</t>
+          <t>Rosa lundlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blitum bonus-henricus</t>
+          <t>Bacidia rosella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rchb.</t>
+          <t>(Pers.) De Not.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nygård, 150 m öster , Sk</t>
+          <t>precis Ö om Nygård, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419169</v>
+        <v>419202</v>
       </c>
       <c r="R2" t="n">
-        <v>6206612</v>
+        <v>6206680</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,19 +738,19 @@
           <t>Häglinge</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M-Hlm-0039</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1990-05-21</t>
+          <t>1993-05-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1990-05-21</t>
+          <t>1993-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sparsamt på 1 bok N om och 1 bok S om vägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,29 +759,265 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bruknngsväg</t>
+          <t>bokskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>bok</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skyddsvärda lavar i sydvästra Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>111315332</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105816</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220711</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lungrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Blitum bonus-henricus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nygård, 150 m öster , Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>419169</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6206612</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Häglinge</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M-Hlm-0039</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1990-05-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1990-05-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bruknngsväg</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86370346</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79737</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6331372</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Liten lundlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bacidina phacodes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Körb.) Vězda</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>precis Ö om Nygård, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>419202</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6206680</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häglinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1993-05-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1993-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sparsamt på 1 bok S om vägen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>bokskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skyddsvärda lavar i sydvästra Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 46602-2023 artfynd.xlsx
+++ b/artfynd/A 46602-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370347</t>
         </is>
       </c>
     </row>
@@ -904,6 +914,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>